--- a/Result/profitability/8084.xlsx
+++ b/Result/profitability/8084.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.91</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1162500000000001</v>
+        <v>0.002500000000000072</v>
       </c>
       <c r="N2" t="n">
-        <v>38.89125</v>
+        <v>38.2725</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.36</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09500000000000008</v>
+        <v>-0.07499999999999993</v>
       </c>
       <c r="N3" t="n">
-        <v>35.78875</v>
+        <v>35.76125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.32</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01250000000000009</v>
+        <v>-0.04624999999999992</v>
       </c>
       <c r="N4" t="n">
-        <v>31.225</v>
+        <v>29.78625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-3.47</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4324999999999999</v>
+        <v>-0.42375</v>
       </c>
       <c r="N5" t="n">
-        <v>20.36375</v>
+        <v>20.115</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.29</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3399999999999999</v>
+        <v>-0.30375</v>
       </c>
       <c r="N6" t="n">
-        <v>15.60625</v>
+        <v>16.61375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.75</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3499999999999999</v>
+        <v>-0.29875</v>
       </c>
       <c r="N7" t="n">
-        <v>11.875</v>
+        <v>11.905</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.71</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3399999999999999</v>
+        <v>-0.42875</v>
       </c>
       <c r="N8" t="n">
-        <v>5.53125</v>
+        <v>4.478750000000002</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -2026,7 +2026,7 @@
         <v>-0.55</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2887499999999999</v>
+        <v>-0.28875</v>
       </c>
       <c r="N13" t="n">
         <v>0.4200000000000008</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8084</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>115</v>
+      </c>
+      <c r="D75" t="n">
+        <v>70</v>
+      </c>
+      <c r="E75" t="n">
+        <v>46</v>
+      </c>
+      <c r="F75" t="n">
+        <v>39.52</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-27</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-23.08%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-34</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-26</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.04499999999999992</v>
+      </c>
+      <c r="N75" t="n">
+        <v>41.86875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-2.151515151515151</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-8.419999999999995</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1756362119315811</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.1555555555555556</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.989999999999995</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.047940255360154</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
